--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.06704604813628</v>
+        <v>7.323394982822147</v>
       </c>
       <c r="D2" t="n">
-        <v>46.07737893984101</v>
+        <v>7.487574077724164</v>
       </c>
       <c r="E2" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F2" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.88262827066641</v>
+        <v>1.768427093983292</v>
       </c>
       <c r="D3" t="n">
-        <v>12.0965991770829</v>
+        <v>1.96569736627597</v>
       </c>
       <c r="E3" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F3" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.00910656170724</v>
+        <v>4.063979816277427</v>
       </c>
       <c r="D4" t="n">
-        <v>25.0262136737405</v>
+        <v>4.066759721982832</v>
       </c>
       <c r="E4" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F4" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.71879165821726</v>
+        <v>6.129303644460304</v>
       </c>
       <c r="D5" t="n">
-        <v>37.86781692643584</v>
+        <v>6.153520250545824</v>
       </c>
       <c r="E5" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F5" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.91557665023869</v>
+        <v>6.161281205663787</v>
       </c>
       <c r="D6" t="n">
-        <v>37.87642914194818</v>
+        <v>6.15491973556658</v>
       </c>
       <c r="E6" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F6" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.3389290729111</v>
+        <v>4.117575974348054</v>
       </c>
       <c r="D7" t="n">
-        <v>26.90186619056654</v>
+        <v>4.371553255967063</v>
       </c>
       <c r="E7" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F7" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.77289907089269</v>
+        <v>2.075596099020062</v>
       </c>
       <c r="D8" t="n">
-        <v>12.07532038742895</v>
+        <v>1.962239562957205</v>
       </c>
       <c r="E8" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F8" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.6661601205039</v>
+        <v>7.908251019581884</v>
       </c>
       <c r="D9" t="n">
-        <v>48.00032321546238</v>
+        <v>7.800052522512637</v>
       </c>
       <c r="E9" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F9" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.32492061755217</v>
+        <v>5.740299600352227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.64075479401072</v>
+        <v>5.629122654026743</v>
       </c>
       <c r="E10" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F10" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52891545396201</v>
+        <v>3.985948761268827</v>
       </c>
       <c r="D11" t="n">
-        <v>23.44552493033898</v>
+        <v>3.809897801180084</v>
       </c>
       <c r="E11" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F11" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.91989945703116</v>
+        <v>3.236983661767563</v>
       </c>
       <c r="D12" t="n">
-        <v>20.21913457044533</v>
+        <v>3.285609367697366</v>
       </c>
       <c r="E12" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F12" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.75274159487378</v>
+        <v>5.647320509166989</v>
       </c>
       <c r="D13" t="n">
-        <v>34.39974665949035</v>
+        <v>5.589958832167182</v>
       </c>
       <c r="E13" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F13" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.42602230697294</v>
+        <v>5.106728624883102</v>
       </c>
       <c r="D14" t="n">
-        <v>31.6719655654299</v>
+        <v>5.146694404382359</v>
       </c>
       <c r="E14" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F14" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.25086624839026</v>
+        <v>4.590765765363417</v>
       </c>
       <c r="D15" t="n">
-        <v>29.07127915201514</v>
+        <v>4.724082862202461</v>
       </c>
       <c r="E15" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F15" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>61.08731458304954</v>
+        <v>9.926688619745551</v>
       </c>
       <c r="D16" t="n">
-        <v>61.82636586932676</v>
+        <v>10.0467844537656</v>
       </c>
       <c r="E16" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F16" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>83.45776630142173</v>
+        <v>13.56188702398103</v>
       </c>
       <c r="D17" t="n">
-        <v>82.90195188022898</v>
+        <v>13.47156718053721</v>
       </c>
       <c r="E17" t="n">
-        <v>17.67203621931626</v>
+        <v>2.871705885638893</v>
       </c>
       <c r="F17" t="n">
-        <v>17.56287557215154</v>
+        <v>2.853967280474625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
